--- a/tiflow-xborder/develop/2.0.0-ballot.2/StructureDefinition-GEM-ERPEU-PR-Consent.xlsx
+++ b/tiflow-xborder/develop/2.0.0-ballot.2/StructureDefinition-GEM-ERPEU-PR-Consent.xlsx
@@ -792,7 +792,7 @@
     <t>A classification of the type of consents found in the statement. This element supports indexing and retrieval of consent statements.</t>
   </si>
   <si>
-    <t>https://gematik.de/fhir/erp-eu/ValueSet/GEM_ERPEU_VS_ConsentType</t>
+    <t>https://gematik.de/fhir/tiflow-xborder/ValueSet/GEM-ERPEU-VS-ConsentType</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1287,7 +1287,7 @@
     <t>Might be a unique identifier of a policy set in XACML, or other rules engine.</t>
   </si>
   <si>
-    <t>https://gematik.de/fhir/erp-eu/ValueSet/GEM_ERPEU_VS_Consent_PolicyRule</t>
+    <t>https://gematik.de/fhir/tiflow-xborder/ValueSet/GEM-ERPEU-VS-Consent-PolicyRule</t>
   </si>
   <si>
     <t>Consent.verification</t>
@@ -1938,7 +1938,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="107.984375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="60.80859375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="65.796875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
